--- a/teach/alunos/Helder/Procv00.xlsx
+++ b/teach/alunos/Helder/Procv00.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Documents\Aniceto\Aula\Helder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Helder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81F288A-E8E5-4ED9-A475-E0C72CABC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF472C4A-D942-4A43-93CB-45B32F162B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
   <si>
     <t>ID</t>
   </si>
@@ -301,15 +301,51 @@
   <si>
     <t>Madrugada</t>
   </si>
+  <si>
+    <t>Relatório de desempenho</t>
+  </si>
+  <si>
+    <t>Analista</t>
+  </si>
+  <si>
+    <t>indice da coluna</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,8 +427,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,6 +479,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -591,10 +661,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -610,34 +681,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -655,12 +699,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -673,46 +716,51 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bom" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -755,13 +803,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -776,6 +817,48 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -787,6 +870,884 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-PT"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2'!$K$8:$P$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>JAN</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FEV</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>MAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ABR</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>MAI</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>JUN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2'!$K$9:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>656</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>124</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F45F-4D4E-BD3A-00CBF2BAF646}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="40588543"/>
+        <c:axId val="40585663"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="40588543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="40585663"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="40585663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="40588543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-PT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1145,12 +2106,109 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>484414</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>402771</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Conector de Seta Reta 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{762D5E27-0388-A3C7-AE44-2A8FFA1A10B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1094014" y="484414"/>
+          <a:ext cx="527957" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>514945</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6547</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>29766</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD279ACB-3891-AA86-6DF7-72AF0468570C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D141FC62-4D41-42DF-9085-C436AAA86AA1}" name="Tabela1" displayName="Tabela1" ref="G4:H8" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D141FC62-4D41-42DF-9085-C436AAA86AA1}" name="Tabela1" displayName="Tabela1" ref="G4:H8" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="G4:H8" xr:uid="{D141FC62-4D41-42DF-9085-C436AAA86AA1}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FC60AAB1-FA42-4A6C-AF4F-253EE67E34F8}" name="HORÁRIO" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{CAAE0D6D-3B21-4581-AB60-0E26CFF2B5D7}" name="TURNO" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{FC60AAB1-FA42-4A6C-AF4F-253EE67E34F8}" name="HORÁRIO" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{CAAE0D6D-3B21-4581-AB60-0E26CFF2B5D7}" name="TURNO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1434,7 +2492,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I2" s="20" t="b">
+      <c r="I2" s="11" t="b">
         <v>0</v>
       </c>
       <c r="J2" s="2">
@@ -1442,13 +2500,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="I3" s="20" t="s">
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36"/>
+      <c r="I3" s="11" t="s">
         <v>40</v>
       </c>
       <c r="J3" s="2">
@@ -1456,22 +2514,22 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="8">
         <v>1</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="8">
         <v>3</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="8">
         <v>4</v>
       </c>
-      <c r="N4" s="22"/>
+      <c r="N4" s="13"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C5" s="4" t="s">
@@ -1489,13 +2547,13 @@
       <c r="H5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I5" s="19">
-        <v>3</v>
-      </c>
-      <c r="J5" s="27" t="s">
+      <c r="I5" s="10">
+        <v>2</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="13" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1517,17 +2575,17 @@
       </c>
       <c r="I6" s="2" t="str">
         <f>VLOOKUP(I$5,$C$5:$F$11,2,FALSE)</f>
-        <v>André</v>
-      </c>
-      <c r="J6" s="28" t="s">
+        <v>Ana</v>
+      </c>
+      <c r="J6" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="30"/>
-      <c r="M6" s="28" t="s">
+      <c r="K6" s="21"/>
+      <c r="M6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="30"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C7" s="2">
@@ -1546,19 +2604,18 @@
       <c r="H7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="27">
         <f>VLOOKUP(I$5,$C$5:$F$11,3,FALSE)</f>
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="J7" s="31" t="s">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="J7" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="33"/>
-      <c r="M7" s="31" t="s">
+      <c r="K7" s="23"/>
+      <c r="M7" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="N7" s="32"/>
-      <c r="O7" s="33"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C8" s="2">
@@ -1579,17 +2636,17 @@
       </c>
       <c r="I8" s="2" t="str">
         <f>VLOOKUP(I$5,$C$5:$F$11,4,FALSE)</f>
-        <v>|</v>
-      </c>
-      <c r="J8" s="34" t="s">
+        <v>||</v>
+      </c>
+      <c r="J8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="36"/>
-      <c r="M8" s="34" t="s">
+      <c r="K8" s="26"/>
+      <c r="M8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="O8" s="36"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="26"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C9" s="2">
@@ -1635,34 +2692,34 @@
       <c r="F11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="I14" s="22" t="s">
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="I14" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="12" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1670,7 +2727,7 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="12"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
@@ -1717,18 +2774,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="22">
+      <c r="G3" s="13">
         <v>1</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="13">
         <v>2</v>
       </c>
     </row>
@@ -1745,10 +2802,10 @@
       <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="31" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1766,10 +2823,10 @@
         <f>VLOOKUP(D5,G$4:H$8,2,1)</f>
         <v>Manhã</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="28">
         <v>0</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="28" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1788,10 +2845,10 @@
         <f t="shared" ref="E6:E10" si="0">VLOOKUP(D6,G$4:H$8,2,1)</f>
         <v>Madrugada</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="28">
         <v>0.29166666666666669</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="H6" s="29" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1810,10 +2867,10 @@
         <f t="shared" si="0"/>
         <v>Tarde</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="28">
         <v>0.58333333333333337</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="29" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1832,10 +2889,10 @@
         <f t="shared" si="0"/>
         <v>Tarde</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="32">
         <v>0.91666666666666663</v>
       </c>
-      <c r="H8" s="43" t="s">
+      <c r="H8" s="33" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1872,7 +2929,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1889,213 +2946,358 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:I10"/>
+  <dimension ref="A2:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="46">
+        <v>1</v>
+      </c>
+      <c r="D3" s="46">
+        <v>2</v>
+      </c>
+      <c r="E3" s="46">
+        <v>3</v>
+      </c>
+      <c r="F3" s="46">
+        <v>4</v>
+      </c>
+      <c r="G3" s="46">
+        <v>5</v>
+      </c>
+      <c r="H3" s="46">
+        <v>6</v>
+      </c>
+      <c r="I3" s="46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="48"/>
+      <c r="C5" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="K6" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D7" s="6">
         <v>234</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E7" s="6">
         <v>186</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F7" s="6">
         <v>656</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G7" s="6">
         <v>667</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H7" s="6">
         <v>117</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I7" s="6">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
-        <f>B5+1</f>
+      <c r="K7" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D8" s="6">
         <v>124</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E8" s="6">
         <v>352</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F8" s="6">
         <v>147</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G8" s="6">
         <v>123</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H8" s="6">
         <v>234</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I8" s="6">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
-        <f t="shared" ref="B7:B9" si="0">B6+1</f>
+      <c r="K8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" ref="B9:B11" si="0">B8+1</f>
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D9" s="6">
         <v>456</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E9" s="6">
         <v>235</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F9" s="6">
         <v>186</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G9" s="6">
         <v>86</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H9" s="6">
         <v>234</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I9" s="6">
         <v>325</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="K9" s="6">
+        <f>VLOOKUP($L7,$C6:$I12,COLUMN(B2),0)</f>
+        <v>234</v>
+      </c>
+      <c r="L9" s="6">
+        <f t="shared" ref="L9:P9" si="1">VLOOKUP($L7,$C6:$I12,COLUMN(C2),0)</f>
+        <v>186</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" si="1"/>
+        <v>656</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" si="1"/>
+        <v>667</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D10" s="6">
         <v>234</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E10" s="6">
         <v>468</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F10" s="6">
         <v>124</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G10" s="6">
         <v>98</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H10" s="6">
         <v>357</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I10" s="6">
         <v>168</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D11" s="6">
         <v>110</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E11" s="6">
         <v>153</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F11" s="6">
         <v>879</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G11" s="6">
         <v>352</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H11" s="6">
         <v>436</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I11" s="6">
         <v>254</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
-        <f>B9+1</f>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2">
+        <f>B11+1</f>
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D12" s="6">
         <v>325</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E12" s="6">
         <v>257</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F12" s="6">
         <v>946</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G12" s="6">
         <v>543</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H12" s="6">
         <v>234</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I12" s="6">
         <v>298</v>
       </c>
     </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K15" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K6:M6"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L7" xr:uid="{FF0C9C94-775A-47D2-8903-4A46BE954E6D}">
+      <formula1>$C$7:$C$12</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2105,125 +3307,125 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="15">
         <v>1</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="15">
         <f>$D3+1</f>
         <v>2</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="15">
         <f t="shared" ref="F3:M3" si="0">$D3+1</f>
         <v>2</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="24">
+      <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="24">
+      <c r="C5" s="15">
         <f>C$4+1</f>
         <v>2</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="3:13" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C6" s="24">
+      <c r="C6" s="15">
         <f t="shared" ref="C6:C13" si="1">C$4+1</f>
         <v>2</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="24">
+      <c r="C7" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="24">
+      <c r="C8" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="24">
+      <c r="C9" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="24">
+      <c r="C10" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="24">
+      <c r="C11" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="24">
+      <c r="C12" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="24">
+      <c r="C13" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
